--- a/data/trans_orig/VUL_MENTALCOM-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/VUL_MENTALCOM-Estudios-trans_orig.xlsx
@@ -651,8 +651,10 @@
           <t>Hasta primaria</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>27</v>
@@ -720,8 +722,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>207</v>
@@ -864,8 +868,10 @@
           <t>Secundaria</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>60</v>
@@ -933,8 +939,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>901</v>
@@ -1077,8 +1085,10 @@
           <t>Estudios universitarios</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>27</v>
@@ -1146,8 +1156,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>430</v>
@@ -1290,8 +1302,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>114</v>
@@ -1359,8 +1373,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>1538</v>
@@ -1734,8 +1750,10 @@
           <t>Hasta primaria</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>47</v>
@@ -1803,8 +1821,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>148</v>
@@ -1947,8 +1967,10 @@
           <t>Secundaria</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>138</v>
@@ -2016,8 +2038,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>657</v>
@@ -2160,8 +2184,10 @@
           <t>Estudios universitarios</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>74</v>
@@ -2229,8 +2255,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>569</v>
@@ -2373,8 +2401,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>259</v>
@@ -2442,8 +2472,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>1374</v>
@@ -2817,8 +2849,10 @@
           <t>Hasta primaria</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>18</v>
@@ -2886,8 +2920,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>425</v>
@@ -3030,8 +3066,10 @@
           <t>Secundaria</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>55</v>
@@ -3099,8 +3137,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>1256</v>
@@ -3243,8 +3283,10 @@
           <t>Estudios universitarios</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>12</v>
@@ -3312,8 +3354,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>557</v>
@@ -3456,8 +3500,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>85</v>
@@ -3525,8 +3571,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>2238</v>
@@ -3900,8 +3948,10 @@
           <t>Hasta primaria</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>27</v>
@@ -3969,8 +4019,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>395</v>
@@ -4113,8 +4165,10 @@
           <t>Secundaria</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>87</v>
@@ -4182,8 +4236,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>2177</v>
@@ -4326,8 +4382,10 @@
           <t>Estudios universitarios</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>22</v>
@@ -4395,8 +4453,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>772</v>
@@ -4539,8 +4599,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>136</v>
@@ -4608,8 +4670,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>3344</v>
